--- a/rrp_multi_round_template.xlsx
+++ b/rrp_multi_round_template.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Round_Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Method_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ChartData_CumReward" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ChartData_TierCells" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ChartData_Runtime" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Charts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData_CumReward" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData_TierCells" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData_Runtime" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -158,14 +158,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -188,14 +188,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -220,14 +220,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -252,14 +252,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -275,6 +275,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'ChartData_CumReward'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ChartData_CumReward'!$A$2:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ChartData_CumReward'!$E$2:$E$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -287,8 +319,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -314,8 +346,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -341,14 +373,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -372,18 +404,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$4</f>
+              <f>'ChartData_TierCells'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$B$2:$B$4</f>
+              <f>'ChartData_TierCells'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -396,18 +428,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$4</f>
+              <f>'ChartData_TierCells'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$C$2:$C$4</f>
+              <f>'ChartData_TierCells'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -420,18 +452,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$4</f>
+              <f>'ChartData_TierCells'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$D$2:$D$4</f>
+              <f>'ChartData_TierCells'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -444,18 +476,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$4</f>
+              <f>'ChartData_TierCells'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$E$2:$E$4</f>
+              <f>'ChartData_TierCells'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -472,8 +504,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -499,8 +531,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -526,14 +558,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -556,14 +588,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -588,14 +620,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -620,14 +652,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -643,6 +675,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'ChartData_Runtime'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ChartData_Runtime'!$A$2:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ChartData_Runtime'!$E$2:$E$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -655,8 +719,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -682,8 +746,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -709,7 +773,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -724,9 +788,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -746,9 +810,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -768,9 +832,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1068,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1164,6 +1228,18 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z61"/>
+  <dimension ref="A1:Z81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1412,16 +1488,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F5" s="3" t="n"/>
@@ -1439,12 +1515,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F6" s="3" t="n"/>
@@ -1462,12 +1538,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F7" s="3" t="n"/>
@@ -1481,16 +1557,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F8" s="3" t="n"/>
@@ -1504,16 +1580,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F9" s="3" t="n"/>
@@ -1531,12 +1607,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F10" s="3" t="n"/>
@@ -1550,16 +1626,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F11" s="3" t="n"/>
@@ -1573,16 +1649,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F12" s="3" t="n"/>
@@ -1596,16 +1672,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F13" s="3" t="n"/>
@@ -1619,7 +1695,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1642,7 +1718,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1665,7 +1741,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1688,16 +1764,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F17" s="3" t="n"/>
@@ -1711,16 +1787,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F18" s="3" t="n"/>
@@ -1734,16 +1810,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F19" s="3" t="n"/>
@@ -1757,16 +1833,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F20" s="3" t="n"/>
@@ -1780,16 +1856,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F21" s="3" t="n"/>
@@ -1803,16 +1879,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F22" s="3" t="n"/>
@@ -1826,16 +1902,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F23" s="3" t="n"/>
@@ -1849,16 +1925,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F24" s="3" t="n"/>
@@ -1872,16 +1948,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F25" s="3" t="n"/>
@@ -1895,7 +1971,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1918,7 +1994,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1941,7 +2017,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1964,16 +2040,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F29" s="3" t="n"/>
@@ -1987,16 +2063,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F30" s="3" t="n"/>
@@ -2010,16 +2086,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F31" s="3" t="n"/>
@@ -2033,16 +2109,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F32" s="3" t="n"/>
@@ -2056,16 +2132,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F33" s="3" t="n"/>
@@ -2079,16 +2155,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F34" s="3" t="n"/>
@@ -2102,16 +2178,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F35" s="3" t="n"/>
@@ -2125,16 +2201,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F36" s="3" t="n"/>
@@ -2148,16 +2224,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F37" s="3" t="n"/>
@@ -2171,7 +2247,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2194,7 +2270,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2217,7 +2293,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2240,16 +2316,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F41" s="3" t="n"/>
@@ -2263,16 +2339,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F42" s="3" t="n"/>
@@ -2286,16 +2362,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F43" s="3" t="n"/>
@@ -2309,16 +2385,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F44" s="3" t="n"/>
@@ -2332,16 +2408,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F45" s="3" t="n"/>
@@ -2355,16 +2431,16 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F46" s="3" t="n"/>
@@ -2378,16 +2454,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F47" s="3" t="n"/>
@@ -2401,16 +2477,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F48" s="3" t="n"/>
@@ -2424,16 +2500,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F49" s="3" t="n"/>
@@ -2447,7 +2523,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2470,7 +2546,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2493,7 +2569,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2516,16 +2592,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F53" s="3" t="n"/>
@@ -2539,16 +2615,16 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F54" s="3" t="n"/>
@@ -2562,16 +2638,16 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F55" s="3" t="n"/>
@@ -2585,16 +2661,16 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F56" s="3" t="n"/>
@@ -2608,16 +2684,16 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F57" s="3" t="n"/>
@@ -2631,16 +2707,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F58" s="3" t="n"/>
@@ -2654,16 +2730,16 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F59" s="3" t="n"/>
@@ -2677,16 +2753,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F60" s="3" t="n"/>
@@ -2700,16 +2776,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F61" s="3" t="n"/>
@@ -2720,6 +2796,466 @@
       <c r="N61" s="3" t="n"/>
       <c r="O61" s="3" t="n"/>
       <c r="P61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>16</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="3" t="n"/>
+      <c r="N62" s="3" t="n"/>
+      <c r="O62" s="3" t="n"/>
+      <c r="P62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>16</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="3" t="n"/>
+      <c r="N63" s="3" t="n"/>
+      <c r="O63" s="3" t="n"/>
+      <c r="P63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>16</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="3" t="n"/>
+      <c r="N64" s="3" t="n"/>
+      <c r="O64" s="3" t="n"/>
+      <c r="P64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>16</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="3" t="n"/>
+      <c r="N65" s="3" t="n"/>
+      <c r="O65" s="3" t="n"/>
+      <c r="P65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>17</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="3" t="n"/>
+      <c r="N66" s="3" t="n"/>
+      <c r="O66" s="3" t="n"/>
+      <c r="P66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>17</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="3" t="n"/>
+      <c r="N67" s="3" t="n"/>
+      <c r="O67" s="3" t="n"/>
+      <c r="P67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>17</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="3" t="n"/>
+      <c r="N68" s="3" t="n"/>
+      <c r="O68" s="3" t="n"/>
+      <c r="P68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>17</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="3" t="n"/>
+      <c r="N69" s="3" t="n"/>
+      <c r="O69" s="3" t="n"/>
+      <c r="P69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>18</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="3" t="n"/>
+      <c r="N70" s="3" t="n"/>
+      <c r="O70" s="3" t="n"/>
+      <c r="P70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>18</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="3" t="n"/>
+      <c r="N71" s="3" t="n"/>
+      <c r="O71" s="3" t="n"/>
+      <c r="P71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>18</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="3" t="n"/>
+      <c r="N72" s="3" t="n"/>
+      <c r="O72" s="3" t="n"/>
+      <c r="P72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>18</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="3" t="n"/>
+      <c r="N73" s="3" t="n"/>
+      <c r="O73" s="3" t="n"/>
+      <c r="P73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>19</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="3" t="n"/>
+      <c r="N74" s="3" t="n"/>
+      <c r="O74" s="3" t="n"/>
+      <c r="P74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>19</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="3" t="n"/>
+      <c r="N75" s="3" t="n"/>
+      <c r="O75" s="3" t="n"/>
+      <c r="P75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>19</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="3" t="n"/>
+      <c r="N76" s="3" t="n"/>
+      <c r="O76" s="3" t="n"/>
+      <c r="P76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>19</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="3" t="n"/>
+      <c r="N77" s="3" t="n"/>
+      <c r="O77" s="3" t="n"/>
+      <c r="P77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>20</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="3" t="n"/>
+      <c r="N78" s="3" t="n"/>
+      <c r="O78" s="3" t="n"/>
+      <c r="P78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>20</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="3" t="n"/>
+      <c r="N79" s="3" t="n"/>
+      <c r="O79" s="3" t="n"/>
+      <c r="P79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>20</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="3" t="n"/>
+      <c r="N80" s="3" t="n"/>
+      <c r="O80" s="3" t="n"/>
+      <c r="P80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="3" t="n"/>
+      <c r="N81" s="3" t="n"/>
+      <c r="O81" s="3" t="n"/>
+      <c r="P81" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2732,7 +3268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2985,6 +3521,62 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="C5" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>MAXIFS(Round_Results!$G:$G,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>AVERAGEIFS(Round_Results!$H:$H,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="3">
+        <f>SUMIFS(Round_Results!$I:$I,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="3">
+        <f>SUMIFS(Round_Results!$J:$J,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
+        <f>MAXIFS(Round_Results!$K:$K,Round_Results!$B:$B,$A5,Round_Results!$A:$A,20)</f>
+        <v/>
+      </c>
+      <c r="J5" s="3">
+        <f>SUMIFS(Round_Results!$U:$U,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
+        <f>SUMIFS(Round_Results!$V:$V,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="3">
+        <f>SUMIFS(Round_Results!$W:$W,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
+        <f>SUMIFS(Round_Results!$X:$X,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2996,7 +3588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3028,6 +3620,11 @@
           <t>RRP_GA</t>
         </is>
       </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3045,6 +3642,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A2)</f>
         <v/>
       </c>
+      <c r="E2" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3062,6 +3663,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A3)</f>
         <v/>
       </c>
+      <c r="E3" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3079,6 +3684,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A4)</f>
         <v/>
       </c>
+      <c r="E4" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3096,6 +3705,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A5)</f>
         <v/>
       </c>
+      <c r="E5" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3113,6 +3726,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A6)</f>
         <v/>
       </c>
+      <c r="E6" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3130,6 +3747,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A7)</f>
         <v/>
       </c>
+      <c r="E7" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3147,6 +3768,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A8)</f>
         <v/>
       </c>
+      <c r="E8" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3164,6 +3789,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A9)</f>
         <v/>
       </c>
+      <c r="E9" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3181,6 +3810,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A10)</f>
         <v/>
       </c>
+      <c r="E10" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3198,6 +3831,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A11)</f>
         <v/>
       </c>
+      <c r="E11" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3215,6 +3852,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A12)</f>
         <v/>
       </c>
+      <c r="E12" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3232,6 +3873,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A13)</f>
         <v/>
       </c>
+      <c r="E13" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3249,6 +3894,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A14)</f>
         <v/>
       </c>
+      <c r="E14" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3266,6 +3915,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A15)</f>
         <v/>
       </c>
+      <c r="E15" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3283,6 +3936,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A16)</f>
         <v/>
       </c>
+      <c r="E16" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3300,6 +3957,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A17)</f>
         <v/>
       </c>
+      <c r="E17" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3317,6 +3978,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A18)</f>
         <v/>
       </c>
+      <c r="E18" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3334,6 +3999,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A19)</f>
         <v/>
       </c>
+      <c r="E19" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3351,6 +4020,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A20)</f>
         <v/>
       </c>
+      <c r="E20" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3366,6 +4039,10 @@
       </c>
       <c r="D21" s="3">
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,D$1,Round_Results!$A:$A,"&lt;="&amp;$A21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A21)</f>
         <v/>
       </c>
     </row>
@@ -3380,7 +4057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3486,6 +4163,29 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>SUMIFS(Round_Results!$U:$U,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>SUMIFS(Round_Results!$V:$V,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>SUMIFS(Round_Results!$W:$W,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>SUMIFS(Round_Results!$X:$X,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3497,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3529,6 +4229,11 @@
           <t>RRP_GA</t>
         </is>
       </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3546,6 +4251,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A2)</f>
         <v/>
       </c>
+      <c r="E2" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3563,6 +4272,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A3)</f>
         <v/>
       </c>
+      <c r="E3" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3580,6 +4293,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A4)</f>
         <v/>
       </c>
+      <c r="E4" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3597,6 +4314,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A5)</f>
         <v/>
       </c>
+      <c r="E5" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3614,6 +4335,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A6)</f>
         <v/>
       </c>
+      <c r="E6" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3631,6 +4356,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A7)</f>
         <v/>
       </c>
+      <c r="E7" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3648,6 +4377,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A8)</f>
         <v/>
       </c>
+      <c r="E8" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3665,6 +4398,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A9)</f>
         <v/>
       </c>
+      <c r="E9" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3682,6 +4419,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A10)</f>
         <v/>
       </c>
+      <c r="E10" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3699,6 +4440,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A11)</f>
         <v/>
       </c>
+      <c r="E11" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3716,6 +4461,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A12)</f>
         <v/>
       </c>
+      <c r="E12" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3733,6 +4482,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A13)</f>
         <v/>
       </c>
+      <c r="E13" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3750,6 +4503,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A14)</f>
         <v/>
       </c>
+      <c r="E14" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3767,6 +4524,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A15)</f>
         <v/>
       </c>
+      <c r="E15" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3784,6 +4545,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A16)</f>
         <v/>
       </c>
+      <c r="E16" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3801,6 +4566,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A17)</f>
         <v/>
       </c>
+      <c r="E17" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3818,6 +4587,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A18)</f>
         <v/>
       </c>
+      <c r="E18" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3835,6 +4608,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A19)</f>
         <v/>
       </c>
+      <c r="E19" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3852,6 +4629,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A20)</f>
         <v/>
       </c>
+      <c r="E20" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3867,6 +4648,10 @@
       </c>
       <c r="D21" s="3">
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,D$1,Round_Results!$A:$A,$A21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A21)</f>
         <v/>
       </c>
     </row>

--- a/rrp_multi_round_template.xlsx
+++ b/rrp_multi_round_template.xlsx
@@ -307,6 +307,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'ChartData_CumReward'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ChartData_CumReward'!$A$2:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ChartData_CumReward'!$F$2:$F$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -410,12 +442,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$5</f>
+              <f>'ChartData_TierCells'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$B$2:$B$5</f>
+              <f>'ChartData_TierCells'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -434,12 +466,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$5</f>
+              <f>'ChartData_TierCells'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$C$2:$C$5</f>
+              <f>'ChartData_TierCells'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -458,12 +490,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$5</f>
+              <f>'ChartData_TierCells'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$D$2:$D$5</f>
+              <f>'ChartData_TierCells'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -482,12 +514,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData_TierCells'!$A$2:$A$5</f>
+              <f>'ChartData_TierCells'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData_TierCells'!$E$2:$E$5</f>
+              <f>'ChartData_TierCells'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -704,6 +736,38 @@
           <val>
             <numRef>
               <f>'ChartData_Runtime'!$E$2:$E$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'ChartData_Runtime'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ChartData_Runtime'!$A$2:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ChartData_Runtime'!$F$2:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -1132,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1222,22 +1286,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>ColumnGeneration</t>
         </is>
@@ -1254,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z81"/>
+  <dimension ref="A1:Z101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1469,12 +1545,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F4" s="3" t="n"/>
@@ -1492,12 +1568,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F5" s="3" t="n"/>
@@ -1511,16 +1587,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F6" s="3" t="n"/>
@@ -1538,12 +1614,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F7" s="3" t="n"/>
@@ -1561,12 +1637,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F8" s="3" t="n"/>
@@ -1584,12 +1660,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F9" s="3" t="n"/>
@@ -1603,16 +1679,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F10" s="3" t="n"/>
@@ -1626,16 +1702,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F11" s="3" t="n"/>
@@ -1653,12 +1729,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F12" s="3" t="n"/>
@@ -1676,12 +1752,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F13" s="3" t="n"/>
@@ -1695,16 +1771,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F14" s="3" t="n"/>
@@ -1718,16 +1794,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F15" s="3" t="n"/>
@@ -1741,16 +1817,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F16" s="3" t="n"/>
@@ -1768,12 +1844,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F17" s="3" t="n"/>
@@ -1787,16 +1863,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F18" s="3" t="n"/>
@@ -1810,16 +1886,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F19" s="3" t="n"/>
@@ -1833,7 +1909,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1856,7 +1932,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1879,7 +1955,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1902,7 +1978,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1925,16 +2001,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F24" s="3" t="n"/>
@@ -1948,16 +2024,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F25" s="3" t="n"/>
@@ -1971,16 +2047,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F26" s="3" t="n"/>
@@ -1994,16 +2070,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F27" s="3" t="n"/>
@@ -2017,16 +2093,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F28" s="3" t="n"/>
@@ -2040,16 +2116,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F29" s="3" t="n"/>
@@ -2063,16 +2139,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F30" s="3" t="n"/>
@@ -2086,16 +2162,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F31" s="3" t="n"/>
@@ -2109,16 +2185,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F32" s="3" t="n"/>
@@ -2132,16 +2208,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F33" s="3" t="n"/>
@@ -2155,16 +2231,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F34" s="3" t="n"/>
@@ -2178,16 +2254,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F35" s="3" t="n"/>
@@ -2201,16 +2277,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F36" s="3" t="n"/>
@@ -2224,16 +2300,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F37" s="3" t="n"/>
@@ -2247,16 +2323,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F38" s="3" t="n"/>
@@ -2270,16 +2346,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F39" s="3" t="n"/>
@@ -2293,7 +2369,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2316,7 +2392,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2339,7 +2415,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2362,7 +2438,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2385,16 +2461,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F44" s="3" t="n"/>
@@ -2408,16 +2484,16 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F45" s="3" t="n"/>
@@ -2431,16 +2507,16 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F46" s="3" t="n"/>
@@ -2454,16 +2530,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F47" s="3" t="n"/>
@@ -2477,16 +2553,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F48" s="3" t="n"/>
@@ -2500,16 +2576,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F49" s="3" t="n"/>
@@ -2523,16 +2599,16 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F50" s="3" t="n"/>
@@ -2546,16 +2622,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F51" s="3" t="n"/>
@@ -2569,16 +2645,16 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F52" s="3" t="n"/>
@@ -2592,16 +2668,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F53" s="3" t="n"/>
@@ -2615,16 +2691,16 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F54" s="3" t="n"/>
@@ -2638,16 +2714,16 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F55" s="3" t="n"/>
@@ -2661,16 +2737,16 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F56" s="3" t="n"/>
@@ -2684,16 +2760,16 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F57" s="3" t="n"/>
@@ -2707,16 +2783,16 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F58" s="3" t="n"/>
@@ -2730,16 +2806,16 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F59" s="3" t="n"/>
@@ -2753,7 +2829,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2776,7 +2852,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2799,7 +2875,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2822,7 +2898,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2845,16 +2921,16 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F64" s="3" t="n"/>
@@ -2868,16 +2944,16 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F65" s="3" t="n"/>
@@ -2891,16 +2967,16 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F66" s="3" t="n"/>
@@ -2914,16 +2990,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F67" s="3" t="n"/>
@@ -2937,16 +3013,16 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F68" s="3" t="n"/>
@@ -2960,16 +3036,16 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F69" s="3" t="n"/>
@@ -2983,16 +3059,16 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F70" s="3" t="n"/>
@@ -3006,16 +3082,16 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F71" s="3" t="n"/>
@@ -3029,16 +3105,16 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F72" s="3" t="n"/>
@@ -3052,16 +3128,16 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F73" s="3" t="n"/>
@@ -3075,16 +3151,16 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F74" s="3" t="n"/>
@@ -3098,16 +3174,16 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F75" s="3" t="n"/>
@@ -3121,16 +3197,16 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_COLUMN_GENERATION</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>ColumnGeneration</t>
         </is>
       </c>
       <c r="F76" s="3" t="n"/>
@@ -3144,16 +3220,16 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_KMEANS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>KMeans</t>
         </is>
       </c>
       <c r="F77" s="3" t="n"/>
@@ -3167,16 +3243,16 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RRP_KMEANS</t>
+          <t>RRP_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KMeans</t>
+          <t>KMeans_VNS</t>
         </is>
       </c>
       <c r="F78" s="3" t="n"/>
@@ -3190,16 +3266,16 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RRP_KMEANS_VNS</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KMeans_VNS</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="F79" s="3" t="n"/>
@@ -3213,7 +3289,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3236,7 +3312,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3256,6 +3332,466 @@
       <c r="N81" s="3" t="n"/>
       <c r="O81" s="3" t="n"/>
       <c r="P81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>17</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="3" t="n"/>
+      <c r="N82" s="3" t="n"/>
+      <c r="O82" s="3" t="n"/>
+      <c r="P82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>17</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="3" t="n"/>
+      <c r="N83" s="3" t="n"/>
+      <c r="O83" s="3" t="n"/>
+      <c r="P83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>17</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>RRP_MS_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MS_KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="3" t="n"/>
+      <c r="N84" s="3" t="n"/>
+      <c r="O84" s="3" t="n"/>
+      <c r="P84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>17</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="3" t="n"/>
+      <c r="H85" s="3" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="3" t="n"/>
+      <c r="N85" s="3" t="n"/>
+      <c r="O85" s="3" t="n"/>
+      <c r="P85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>17</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="3" t="n"/>
+      <c r="N86" s="3" t="n"/>
+      <c r="O86" s="3" t="n"/>
+      <c r="P86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>18</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="L87" s="4" t="n"/>
+      <c r="M87" s="3" t="n"/>
+      <c r="N87" s="3" t="n"/>
+      <c r="O87" s="3" t="n"/>
+      <c r="P87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>18</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="L88" s="4" t="n"/>
+      <c r="M88" s="3" t="n"/>
+      <c r="N88" s="3" t="n"/>
+      <c r="O88" s="3" t="n"/>
+      <c r="P88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>18</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RRP_MS_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MS_KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="3" t="n"/>
+      <c r="N89" s="3" t="n"/>
+      <c r="O89" s="3" t="n"/>
+      <c r="P89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>18</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="3" t="n"/>
+      <c r="N90" s="3" t="n"/>
+      <c r="O90" s="3" t="n"/>
+      <c r="P90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>18</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="L91" s="4" t="n"/>
+      <c r="M91" s="3" t="n"/>
+      <c r="N91" s="3" t="n"/>
+      <c r="O91" s="3" t="n"/>
+      <c r="P91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>19</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="L92" s="4" t="n"/>
+      <c r="M92" s="3" t="n"/>
+      <c r="N92" s="3" t="n"/>
+      <c r="O92" s="3" t="n"/>
+      <c r="P92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>19</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="3" t="n"/>
+      <c r="N93" s="3" t="n"/>
+      <c r="O93" s="3" t="n"/>
+      <c r="P93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>19</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RRP_MS_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MS_KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="n"/>
+      <c r="O94" s="3" t="n"/>
+      <c r="P94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>19</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="3" t="n"/>
+      <c r="N95" s="3" t="n"/>
+      <c r="O95" s="3" t="n"/>
+      <c r="P95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>19</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="3" t="n"/>
+      <c r="N96" s="3" t="n"/>
+      <c r="O96" s="3" t="n"/>
+      <c r="P96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>20</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>KMeans</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="3" t="n"/>
+      <c r="H97" s="3" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="3" t="n"/>
+      <c r="N97" s="3" t="n"/>
+      <c r="O97" s="3" t="n"/>
+      <c r="P97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>20</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>RRP_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n"/>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="3" t="n"/>
+      <c r="N98" s="3" t="n"/>
+      <c r="O98" s="3" t="n"/>
+      <c r="P98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>20</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>RRP_MS_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MS_KMeans_VNS</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="3" t="n"/>
+      <c r="H99" s="3" t="n"/>
+      <c r="L99" s="4" t="n"/>
+      <c r="M99" s="3" t="n"/>
+      <c r="N99" s="3" t="n"/>
+      <c r="O99" s="3" t="n"/>
+      <c r="P99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>20</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>RRP_GA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="3" t="n"/>
+      <c r="N100" s="3" t="n"/>
+      <c r="O100" s="3" t="n"/>
+      <c r="P100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>20</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n"/>
+      <c r="G101" s="3" t="n"/>
+      <c r="H101" s="3" t="n"/>
+      <c r="L101" s="4" t="n"/>
+      <c r="M101" s="3" t="n"/>
+      <c r="N101" s="3" t="n"/>
+      <c r="O101" s="3" t="n"/>
+      <c r="P101" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3268,7 +3804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3468,12 +4004,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>MS_KMeans_VNS</t>
         </is>
       </c>
       <c r="C4" s="3">
@@ -3524,12 +4060,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="C5" s="3">
@@ -3574,6 +4110,62 @@
       </c>
       <c r="M5" s="3">
         <f>SUMIFS(Round_Results!$X:$X,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ColumnGeneration</t>
+        </is>
+      </c>
+      <c r="C6" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>MAXIFS(Round_Results!$G:$G,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="3">
+        <f>AVERAGEIFS(Round_Results!$H:$H,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="3">
+        <f>SUMIFS(Round_Results!$I:$I,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="3">
+        <f>SUMIFS(Round_Results!$J:$J,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="3">
+        <f>MAXIFS(Round_Results!$K:$K,Round_Results!$B:$B,$A6,Round_Results!$A:$A,20)</f>
+        <v/>
+      </c>
+      <c r="J6" s="3">
+        <f>SUMIFS(Round_Results!$U:$U,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>SUMIFS(Round_Results!$V:$V,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="3">
+        <f>SUMIFS(Round_Results!$W:$W,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
+        <f>SUMIFS(Round_Results!$X:$X,Round_Results!$B:$B,$A6)</f>
         <v/>
       </c>
     </row>
@@ -3588,7 +4180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3617,10 +4209,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>RRP_MS_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>RRP_GA</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>RRP_COLUMN_GENERATION</t>
         </is>
@@ -3646,6 +4243,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A2)</f>
         <v/>
       </c>
+      <c r="F2" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3667,6 +4268,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A3)</f>
         <v/>
       </c>
+      <c r="F3" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3688,6 +4293,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A4)</f>
         <v/>
       </c>
+      <c r="F4" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3709,6 +4318,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A5)</f>
         <v/>
       </c>
+      <c r="F5" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3730,6 +4343,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A6)</f>
         <v/>
       </c>
+      <c r="F6" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3751,6 +4368,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A7)</f>
         <v/>
       </c>
+      <c r="F7" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3772,6 +4393,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A8)</f>
         <v/>
       </c>
+      <c r="F8" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3793,6 +4418,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A9)</f>
         <v/>
       </c>
+      <c r="F9" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3814,6 +4443,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A10)</f>
         <v/>
       </c>
+      <c r="F10" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3835,6 +4468,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A11)</f>
         <v/>
       </c>
+      <c r="F11" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3856,6 +4493,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A12)</f>
         <v/>
       </c>
+      <c r="F12" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3877,6 +4518,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A13)</f>
         <v/>
       </c>
+      <c r="F13" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3898,6 +4543,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A14)</f>
         <v/>
       </c>
+      <c r="F14" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3919,6 +4568,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A15)</f>
         <v/>
       </c>
+      <c r="F15" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3940,6 +4593,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A16)</f>
         <v/>
       </c>
+      <c r="F16" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3961,6 +4618,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A17)</f>
         <v/>
       </c>
+      <c r="F17" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3982,6 +4643,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A18)</f>
         <v/>
       </c>
+      <c r="F18" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4003,6 +4668,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A19)</f>
         <v/>
       </c>
+      <c r="F19" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4024,6 +4693,10 @@
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A20)</f>
         <v/>
       </c>
+      <c r="F20" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4043,6 +4716,10 @@
       </c>
       <c r="E21" s="3">
         <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,E$1,Round_Results!$A:$A,"&lt;="&amp;$A21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>SUMIFS(Round_Results!$F:$F,Round_Results!$B:$B,F$1,Round_Results!$A:$A,"&lt;="&amp;$A21)</f>
         <v/>
       </c>
     </row>
@@ -4057,7 +4734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4143,7 +4820,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RRP_GA</t>
+          <t>RRP_MS_KMEANS_VNS</t>
         </is>
       </c>
       <c r="B4" s="3">
@@ -4166,7 +4843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_GA</t>
         </is>
       </c>
       <c r="B5" s="3">
@@ -4183,6 +4860,29 @@
       </c>
       <c r="E5" s="3">
         <f>SUMIFS(Round_Results!$X:$X,Round_Results!$B:$B,$A5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RRP_COLUMN_GENERATION</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>SUMIFS(Round_Results!$U:$U,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>SUMIFS(Round_Results!$V:$V,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>SUMIFS(Round_Results!$W:$W,Round_Results!$B:$B,$A6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUMIFS(Round_Results!$X:$X,Round_Results!$B:$B,$A6)</f>
         <v/>
       </c>
     </row>
@@ -4197,7 +4897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4226,10 +4926,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>RRP_MS_KMEANS_VNS</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>RRP_GA</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>RRP_COLUMN_GENERATION</t>
         </is>
@@ -4255,6 +4960,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A2)</f>
         <v/>
       </c>
+      <c r="F2" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4276,6 +4985,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A3)</f>
         <v/>
       </c>
+      <c r="F3" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4297,6 +5010,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A4)</f>
         <v/>
       </c>
+      <c r="F4" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4318,6 +5035,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A5)</f>
         <v/>
       </c>
+      <c r="F5" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4339,6 +5060,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A6)</f>
         <v/>
       </c>
+      <c r="F6" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4360,6 +5085,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A7)</f>
         <v/>
       </c>
+      <c r="F7" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4381,6 +5110,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A8)</f>
         <v/>
       </c>
+      <c r="F8" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4402,6 +5135,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A9)</f>
         <v/>
       </c>
+      <c r="F9" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4423,6 +5160,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A10)</f>
         <v/>
       </c>
+      <c r="F10" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4444,6 +5185,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A11)</f>
         <v/>
       </c>
+      <c r="F11" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4465,6 +5210,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A12)</f>
         <v/>
       </c>
+      <c r="F12" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4486,6 +5235,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A13)</f>
         <v/>
       </c>
+      <c r="F13" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4507,6 +5260,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A14)</f>
         <v/>
       </c>
+      <c r="F14" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4528,6 +5285,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A15)</f>
         <v/>
       </c>
+      <c r="F15" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4549,6 +5310,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A16)</f>
         <v/>
       </c>
+      <c r="F16" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4570,6 +5335,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A17)</f>
         <v/>
       </c>
+      <c r="F17" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4591,6 +5360,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A18)</f>
         <v/>
       </c>
+      <c r="F18" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4612,6 +5385,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A19)</f>
         <v/>
       </c>
+      <c r="F19" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4633,6 +5410,10 @@
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A20)</f>
         <v/>
       </c>
+      <c r="F20" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4652,6 +5433,10 @@
       </c>
       <c r="E21" s="3">
         <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,E$1,Round_Results!$A:$A,$A21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>SUMIFS(Round_Results!$H:$H,Round_Results!$B:$B,F$1,Round_Results!$A:$A,$A21)</f>
         <v/>
       </c>
     </row>

--- a/rrp_multi_round_template.xlsx
+++ b/rrp_multi_round_template.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Round_Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData_CumReward" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData_TierCells" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData_Runtime" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Round_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Method_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ChartData_CumReward" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ChartData_TierCells" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ChartData_Runtime" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Charts" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -158,14 +158,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -188,14 +188,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -220,14 +220,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -252,14 +252,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -284,14 +284,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -316,14 +316,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -351,8 +351,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -378,8 +378,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -405,14 +405,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -436,7 +436,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -460,7 +460,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -484,7 +484,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -508,7 +508,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -536,8 +536,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -563,8 +563,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -590,14 +590,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -620,14 +620,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -652,14 +652,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -684,14 +684,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -716,14 +716,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -748,14 +748,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -783,8 +783,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -810,8 +810,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -837,7 +837,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -852,9 +852,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -874,9 +874,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -896,9 +896,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1310,12 +1310,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1359,6 +1359,8 @@
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="28" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1490,6 +1492,16 @@
       <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>n_columns</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>gurobi_gap</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>n_feasible_groups</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1603,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" s="3" t="n"/>
@@ -1706,12 +1718,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" s="3" t="n"/>
@@ -1821,12 +1833,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" s="3" t="n"/>
@@ -1936,12 +1948,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" s="3" t="n"/>
@@ -2051,12 +2063,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" s="3" t="n"/>
@@ -2166,12 +2178,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" s="3" t="n"/>
@@ -2281,12 +2293,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" s="3" t="n"/>
@@ -2396,12 +2408,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" s="3" t="n"/>
@@ -2511,12 +2523,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" s="3" t="n"/>
@@ -2626,12 +2638,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" s="3" t="n"/>
@@ -2741,12 +2753,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" s="3" t="n"/>
@@ -2856,12 +2868,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" s="3" t="n"/>
@@ -2971,12 +2983,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" s="3" t="n"/>
@@ -3086,12 +3098,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" s="3" t="n"/>
@@ -3201,12 +3213,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" s="3" t="n"/>
@@ -3316,12 +3328,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" s="3" t="n"/>
@@ -3431,12 +3443,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" s="3" t="n"/>
@@ -3546,12 +3558,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" s="3" t="n"/>
@@ -3661,12 +3673,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" s="3" t="n"/>
@@ -3776,12 +3788,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" s="3" t="n"/>
@@ -4116,12 +4128,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ColumnGeneration</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C6" s="3">
@@ -4219,7 +4231,7 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
       <c r="B6" s="3">
@@ -4936,7 +4948,7 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>RRP_COLUMN_GENERATION</t>
+          <t>RRP_SA</t>
         </is>
       </c>
     </row>
